--- a/rooftopadmin/sample_files/sample_customer_excel.xlsx
+++ b/rooftopadmin/sample_files/sample_customer_excel.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ps_projects\vtech\admin\sample_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\vtech\rooftopadmin\sample_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE9566A7-17BC-4B7A-9645-18D02412ACC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11670" windowHeight="4575"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main Sheet" sheetId="1" r:id="rId1"/>
@@ -50,9 +51,6 @@
     <t>State</t>
   </si>
   <si>
-    <t>Pump Capacity</t>
-  </si>
-  <si>
     <t>Work Order No</t>
   </si>
   <si>
@@ -63,12 +61,15 @@
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>Rooftop  Capacity</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -386,14 +387,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="16" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -419,30 +420,30 @@
         <v>4</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>1</v>
